--- a/y12907/test-output/安全拒答样本归因分析_测试导出.xlsx
+++ b/y12907/test-output/安全拒答样本归因分析_测试导出.xlsx
@@ -416,7 +416,7 @@
         <v>分析时间</v>
       </c>
       <c r="B3" t="str">
-        <v>2026/6/17 23:27:51</v>
+        <v>2026/6/18 03:05:22</v>
       </c>
     </row>
     <row r="4">
@@ -424,7 +424,7 @@
         <v>运行编号</v>
       </c>
       <c r="B4" t="str">
-        <v>RUN-1781706471635-test123</v>
+        <v>RUN-1781719523030-test123</v>
       </c>
     </row>
     <row r="5">
